--- a/retail-ai-platform/docs/samples/SYNTHETIC_HC_sales_2026-07-01_2026-09-30.xlsx
+++ b/retail-ai-platform/docs/samples/SYNTHETIC_HC_sales_2026-07-01_2026-09-30.xlsx
@@ -539,7 +539,7 @@
         <v>58333</v>
       </c>
       <c r="J2" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>120000</v>
       </c>
       <c r="J3" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -643,7 +643,7 @@
         <v>55417</v>
       </c>
       <c r="J4" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K4" t="n">
         <v>3500</v>
@@ -695,7 +695,7 @@
         <v>84583</v>
       </c>
       <c r="J5" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K5" t="n">
         <v>3500</v>
@@ -747,7 +747,7 @@
         <v>10875</v>
       </c>
       <c r="J6" t="n">
-        <v>15660</v>
+        <v>13050</v>
       </c>
       <c r="K6" t="n">
         <v>450</v>
@@ -799,7 +799,7 @@
         <v>87500</v>
       </c>
       <c r="J7" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>7500</v>
       </c>
       <c r="J8" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>40000</v>
       </c>
       <c r="J9" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
         <v>76000</v>
       </c>
       <c r="J10" t="n">
-        <v>109440</v>
+        <v>91200</v>
       </c>
       <c r="K10" t="n">
         <v>4800</v>
@@ -1007,7 +1007,7 @@
         <v>29167</v>
       </c>
       <c r="J11" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>7500</v>
       </c>
       <c r="J12" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>3750</v>
       </c>
       <c r="J13" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>36000</v>
       </c>
       <c r="J14" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K14" t="n">
         <v>4800</v>
@@ -1215,7 +1215,7 @@
         <v>11250</v>
       </c>
       <c r="J15" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>7125</v>
       </c>
       <c r="J16" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K16" t="n">
         <v>450</v>
@@ -1319,7 +1319,7 @@
         <v>29167</v>
       </c>
       <c r="J17" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>40000</v>
       </c>
       <c r="J19" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>58333</v>
       </c>
       <c r="J20" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>20000</v>
       </c>
       <c r="J21" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>58333</v>
       </c>
       <c r="J22" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>10000</v>
       </c>
       <c r="J23" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>29167</v>
       </c>
       <c r="J24" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>3750</v>
       </c>
       <c r="J25" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>11250</v>
       </c>
       <c r="J26" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>29000</v>
       </c>
       <c r="J27" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K27" t="n">
         <v>1200</v>
@@ -1891,7 +1891,7 @@
         <v>9000</v>
       </c>
       <c r="J28" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K28" t="n">
         <v>1200</v>
@@ -1943,7 +1943,7 @@
         <v>29167</v>
       </c>
       <c r="J29" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>87500</v>
       </c>
       <c r="J31" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>3750</v>
       </c>
       <c r="J32" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>120000</v>
       </c>
       <c r="J33" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>55417</v>
       </c>
       <c r="J34" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K34" t="n">
         <v>3500</v>
@@ -2255,7 +2255,7 @@
         <v>40000</v>
       </c>
       <c r="J35" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>80000</v>
       </c>
       <c r="J36" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>87500</v>
       </c>
       <c r="J37" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>120000</v>
       </c>
       <c r="J38" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         <v>87500</v>
       </c>
       <c r="J39" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>58333</v>
       </c>
       <c r="J40" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>55417</v>
       </c>
       <c r="J41" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K41" t="n">
         <v>3500</v>
@@ -2619,7 +2619,7 @@
         <v>7125</v>
       </c>
       <c r="J42" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K42" t="n">
         <v>450</v>
@@ -2723,7 +2723,7 @@
         <v>58333</v>
       </c>
       <c r="J44" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>30000</v>
       </c>
       <c r="J45" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>30000</v>
       </c>
       <c r="J46" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>30000</v>
       </c>
       <c r="J47" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
         <v>20000</v>
       </c>
       <c r="J48" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>84583</v>
       </c>
       <c r="J49" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K49" t="n">
         <v>3500</v>
@@ -3035,7 +3035,7 @@
         <v>40000</v>
       </c>
       <c r="J50" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>11250</v>
       </c>
       <c r="J51" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>29167</v>
       </c>
       <c r="J52" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>116000</v>
       </c>
       <c r="J53" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K53" t="n">
         <v>4800</v>
@@ -3243,7 +3243,7 @@
         <v>76000</v>
       </c>
       <c r="J54" t="n">
-        <v>109440</v>
+        <v>91200</v>
       </c>
       <c r="K54" t="n">
         <v>4800</v>
@@ -3295,7 +3295,7 @@
         <v>11250</v>
       </c>
       <c r="J55" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
         <v>3750</v>
       </c>
       <c r="J56" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
         <v>3750</v>
       </c>
       <c r="J57" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -3451,7 +3451,7 @@
         <v>3750</v>
       </c>
       <c r="J58" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>58333</v>
       </c>
       <c r="J60" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3607,7 +3607,7 @@
         <v>29000</v>
       </c>
       <c r="J61" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K61" t="n">
         <v>1200</v>
@@ -3659,7 +3659,7 @@
         <v>9000</v>
       </c>
       <c r="J62" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K62" t="n">
         <v>1200</v>
@@ -3711,7 +3711,7 @@
         <v>20000</v>
       </c>
       <c r="J63" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>29167</v>
       </c>
       <c r="J64" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>58333</v>
       </c>
       <c r="J65" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>55417</v>
       </c>
       <c r="J66" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K66" t="n">
         <v>3500</v>
@@ -3919,7 +3919,7 @@
         <v>84583</v>
       </c>
       <c r="J67" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K67" t="n">
         <v>3500</v>
@@ -3971,7 +3971,7 @@
         <v>10000</v>
       </c>
       <c r="J68" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>116000</v>
       </c>
       <c r="J69" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K69" t="n">
         <v>4800</v>
@@ -4075,7 +4075,7 @@
         <v>20000</v>
       </c>
       <c r="J70" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         <v>29167</v>
       </c>
       <c r="J71" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>58333</v>
       </c>
       <c r="J72" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>9000</v>
       </c>
       <c r="J73" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K73" t="n">
         <v>1200</v>
@@ -4283,7 +4283,7 @@
         <v>10000</v>
       </c>
       <c r="J74" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
         <v>40000</v>
       </c>
       <c r="J75" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>58333</v>
       </c>
       <c r="J76" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>3750</v>
       </c>
       <c r="J77" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>58333</v>
       </c>
       <c r="J78" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         <v>120000</v>
       </c>
       <c r="J79" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>30000</v>
       </c>
       <c r="J80" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>29167</v>
       </c>
       <c r="J81" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>58333</v>
       </c>
       <c r="J82" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -4751,7 +4751,7 @@
         <v>7500</v>
       </c>
       <c r="J83" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>40000</v>
       </c>
       <c r="J84" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
         <v>29167</v>
       </c>
       <c r="J85" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
         <v>26250</v>
       </c>
       <c r="J86" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K86" t="n">
         <v>3500</v>
@@ -4959,7 +4959,7 @@
         <v>36000</v>
       </c>
       <c r="J87" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K87" t="n">
         <v>4800</v>
@@ -5011,7 +5011,7 @@
         <v>80000</v>
       </c>
       <c r="J88" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>58333</v>
       </c>
       <c r="J89" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>120000</v>
       </c>
       <c r="J91" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>58333</v>
       </c>
       <c r="J92" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3375</v>
       </c>
       <c r="J93" t="n">
-        <v>4860</v>
+        <v>4050</v>
       </c>
       <c r="K93" t="n">
         <v>450</v>
@@ -5323,7 +5323,7 @@
         <v>120000</v>
       </c>
       <c r="J94" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
         <v>7500</v>
       </c>
       <c r="J95" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -5427,7 +5427,7 @@
         <v>84583</v>
       </c>
       <c r="J96" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K96" t="n">
         <v>3500</v>
@@ -5479,7 +5479,7 @@
         <v>11250</v>
       </c>
       <c r="J97" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>29167</v>
       </c>
       <c r="J98" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
         <v>87500</v>
       </c>
       <c r="J99" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>58333</v>
       </c>
       <c r="J100" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -5687,7 +5687,7 @@
         <v>40000</v>
       </c>
       <c r="J101" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
         <v>84583</v>
       </c>
       <c r="J102" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K102" t="n">
         <v>3500</v>
@@ -5791,7 +5791,7 @@
         <v>58333</v>
       </c>
       <c r="J103" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
         <v>87500</v>
       </c>
       <c r="J104" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -5895,7 +5895,7 @@
         <v>120000</v>
       </c>
       <c r="J105" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>20000</v>
       </c>
       <c r="J107" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
         <v>10000</v>
       </c>
       <c r="J108" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -6103,7 +6103,7 @@
         <v>10000</v>
       </c>
       <c r="J109" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>80000</v>
       </c>
       <c r="J110" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>3750</v>
       </c>
       <c r="J111" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>87500</v>
       </c>
       <c r="J112" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
         <v>55417</v>
       </c>
       <c r="J113" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K113" t="n">
         <v>3500</v>
@@ -6363,7 +6363,7 @@
         <v>26250</v>
       </c>
       <c r="J114" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K114" t="n">
         <v>3500</v>
@@ -6415,7 +6415,7 @@
         <v>19000</v>
       </c>
       <c r="J115" t="n">
-        <v>27360</v>
+        <v>22800</v>
       </c>
       <c r="K115" t="n">
         <v>1200</v>
@@ -6467,7 +6467,7 @@
         <v>40000</v>
       </c>
       <c r="J116" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>29167</v>
       </c>
       <c r="J117" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>30000</v>
       </c>
       <c r="J118" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>40000</v>
       </c>
       <c r="J119" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>120000</v>
       </c>
       <c r="J120" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
         <v>30000</v>
       </c>
       <c r="J121" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>9000</v>
       </c>
       <c r="J122" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K122" t="n">
         <v>1200</v>
@@ -6883,7 +6883,7 @@
         <v>80000</v>
       </c>
       <c r="J124" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -6935,7 +6935,7 @@
         <v>20000</v>
       </c>
       <c r="J125" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>120000</v>
       </c>
       <c r="J126" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>29167</v>
       </c>
       <c r="J127" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -7091,7 +7091,7 @@
         <v>7500</v>
       </c>
       <c r="J128" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -7143,7 +7143,7 @@
         <v>20000</v>
       </c>
       <c r="J129" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>29167</v>
       </c>
       <c r="J130" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>58333</v>
       </c>
       <c r="J131" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         <v>20000</v>
       </c>
       <c r="J132" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>36000</v>
       </c>
       <c r="J133" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K133" t="n">
         <v>4800</v>
@@ -7403,7 +7403,7 @@
         <v>87500</v>
       </c>
       <c r="J134" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>55417</v>
       </c>
       <c r="J135" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K135" t="n">
         <v>3500</v>
@@ -7507,7 +7507,7 @@
         <v>40000</v>
       </c>
       <c r="J136" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>7500</v>
       </c>
       <c r="J137" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -7611,7 +7611,7 @@
         <v>7125</v>
       </c>
       <c r="J138" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K138" t="n">
         <v>450</v>
@@ -7663,7 +7663,7 @@
         <v>29167</v>
       </c>
       <c r="J139" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         <v>87500</v>
       </c>
       <c r="J140" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -7767,7 +7767,7 @@
         <v>87500</v>
       </c>
       <c r="J141" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -7819,7 +7819,7 @@
         <v>29167</v>
       </c>
       <c r="J142" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -7871,7 +7871,7 @@
         <v>20000</v>
       </c>
       <c r="J143" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -7923,7 +7923,7 @@
         <v>7125</v>
       </c>
       <c r="J144" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K144" t="n">
         <v>450</v>
@@ -7975,7 +7975,7 @@
         <v>58333</v>
       </c>
       <c r="J145" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>30000</v>
       </c>
       <c r="J146" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         <v>58333</v>
       </c>
       <c r="J147" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -8131,7 +8131,7 @@
         <v>58333</v>
       </c>
       <c r="J148" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -8183,7 +8183,7 @@
         <v>116000</v>
       </c>
       <c r="J149" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K149" t="n">
         <v>4800</v>
@@ -8235,7 +8235,7 @@
         <v>120000</v>
       </c>
       <c r="J150" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
         <v>58333</v>
       </c>
       <c r="J151" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -8339,7 +8339,7 @@
         <v>84583</v>
       </c>
       <c r="J152" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K152" t="n">
         <v>3500</v>
@@ -8391,7 +8391,7 @@
         <v>20000</v>
       </c>
       <c r="J153" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
         <v>29167</v>
       </c>
       <c r="J154" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -8495,7 +8495,7 @@
         <v>87500</v>
       </c>
       <c r="J155" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>29167</v>
       </c>
       <c r="J156" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -8599,7 +8599,7 @@
         <v>84583</v>
       </c>
       <c r="J157" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K157" t="n">
         <v>3500</v>
@@ -8651,7 +8651,7 @@
         <v>20000</v>
       </c>
       <c r="J158" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v>29167</v>
       </c>
       <c r="J159" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>3375</v>
       </c>
       <c r="J160" t="n">
-        <v>4860</v>
+        <v>4050</v>
       </c>
       <c r="K160" t="n">
         <v>450</v>
@@ -8807,7 +8807,7 @@
         <v>10000</v>
       </c>
       <c r="J161" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>58333</v>
       </c>
       <c r="J162" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -8911,7 +8911,7 @@
         <v>9000</v>
       </c>
       <c r="J163" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K163" t="n">
         <v>1200</v>
@@ -8963,7 +8963,7 @@
         <v>58333</v>
       </c>
       <c r="J164" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -9015,7 +9015,7 @@
         <v>87500</v>
       </c>
       <c r="J165" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
         <v>80000</v>
       </c>
       <c r="J166" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -9119,7 +9119,7 @@
         <v>87500</v>
       </c>
       <c r="J167" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>55417</v>
       </c>
       <c r="J168" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K168" t="n">
         <v>3500</v>
@@ -9223,7 +9223,7 @@
         <v>20000</v>
       </c>
       <c r="J169" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
         <v>87500</v>
       </c>
       <c r="J170" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -9327,7 +9327,7 @@
         <v>20000</v>
       </c>
       <c r="J171" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -9379,7 +9379,7 @@
         <v>26250</v>
       </c>
       <c r="J172" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K172" t="n">
         <v>3500</v>
@@ -9431,7 +9431,7 @@
         <v>30000</v>
       </c>
       <c r="J173" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -9483,7 +9483,7 @@
         <v>29167</v>
       </c>
       <c r="J174" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
         <v>26250</v>
       </c>
       <c r="J176" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K176" t="n">
         <v>3500</v>
@@ -9639,7 +9639,7 @@
         <v>11250</v>
       </c>
       <c r="J177" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
         <v>120000</v>
       </c>
       <c r="J178" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -9743,7 +9743,7 @@
         <v>10000</v>
       </c>
       <c r="J179" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -9795,7 +9795,7 @@
         <v>58333</v>
       </c>
       <c r="J180" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -9847,7 +9847,7 @@
         <v>20000</v>
       </c>
       <c r="J181" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -9899,7 +9899,7 @@
         <v>26250</v>
       </c>
       <c r="J182" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K182" t="n">
         <v>3500</v>
@@ -9951,7 +9951,7 @@
         <v>40000</v>
       </c>
       <c r="J183" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>120000</v>
       </c>
       <c r="J185" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
         <v>29167</v>
       </c>
       <c r="J186" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -10159,7 +10159,7 @@
         <v>29167</v>
       </c>
       <c r="J187" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
         <v>55417</v>
       </c>
       <c r="J188" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K188" t="n">
         <v>3500</v>
@@ -10263,7 +10263,7 @@
         <v>7500</v>
       </c>
       <c r="J189" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -10315,7 +10315,7 @@
         <v>58333</v>
       </c>
       <c r="J190" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
         <v>3750</v>
       </c>
       <c r="J191" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -10419,7 +10419,7 @@
         <v>20000</v>
       </c>
       <c r="J192" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -10471,7 +10471,7 @@
         <v>120000</v>
       </c>
       <c r="J193" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
         <v>58333</v>
       </c>
       <c r="J194" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -10575,7 +10575,7 @@
         <v>9000</v>
       </c>
       <c r="J195" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K195" t="n">
         <v>1200</v>
@@ -10627,7 +10627,7 @@
         <v>30000</v>
       </c>
       <c r="J196" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -10679,7 +10679,7 @@
         <v>3375</v>
       </c>
       <c r="J197" t="n">
-        <v>4860</v>
+        <v>4050</v>
       </c>
       <c r="K197" t="n">
         <v>450</v>
@@ -10731,7 +10731,7 @@
         <v>3750</v>
       </c>
       <c r="J198" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
         <v>26250</v>
       </c>
       <c r="J199" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K199" t="n">
         <v>3500</v>
@@ -10835,7 +10835,7 @@
         <v>40000</v>
       </c>
       <c r="J200" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>84583</v>
       </c>
       <c r="J201" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K201" t="n">
         <v>3500</v>
@@ -10939,7 +10939,7 @@
         <v>7500</v>
       </c>
       <c r="J202" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -10991,7 +10991,7 @@
         <v>3750</v>
       </c>
       <c r="J203" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
         <v>20000</v>
       </c>
       <c r="J204" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>87500</v>
       </c>
       <c r="J205" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -11147,7 +11147,7 @@
         <v>29000</v>
       </c>
       <c r="J206" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K206" t="n">
         <v>1200</v>
@@ -11199,7 +11199,7 @@
         <v>120000</v>
       </c>
       <c r="J207" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -11251,7 +11251,7 @@
         <v>7500</v>
       </c>
       <c r="J208" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>7125</v>
       </c>
       <c r="J209" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K209" t="n">
         <v>450</v>
@@ -11355,7 +11355,7 @@
         <v>7500</v>
       </c>
       <c r="J210" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -11407,7 +11407,7 @@
         <v>29167</v>
       </c>
       <c r="J211" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -11459,7 +11459,7 @@
         <v>36000</v>
       </c>
       <c r="J212" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K212" t="n">
         <v>4800</v>
@@ -11511,7 +11511,7 @@
         <v>120000</v>
       </c>
       <c r="J213" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>29167</v>
       </c>
       <c r="J214" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -11615,7 +11615,7 @@
         <v>40000</v>
       </c>
       <c r="J215" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         <v>7500</v>
       </c>
       <c r="J216" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         <v>10000</v>
       </c>
       <c r="J217" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>7500</v>
       </c>
       <c r="J218" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -11823,7 +11823,7 @@
         <v>29167</v>
       </c>
       <c r="J219" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -11875,7 +11875,7 @@
         <v>80000</v>
       </c>
       <c r="J220" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -11927,7 +11927,7 @@
         <v>3750</v>
       </c>
       <c r="J221" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -11979,7 +11979,7 @@
         <v>116000</v>
       </c>
       <c r="J222" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K222" t="n">
         <v>4800</v>
@@ -12031,7 +12031,7 @@
         <v>20000</v>
       </c>
       <c r="J223" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -12083,7 +12083,7 @@
         <v>29167</v>
       </c>
       <c r="J224" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -12135,7 +12135,7 @@
         <v>120000</v>
       </c>
       <c r="J225" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -12187,7 +12187,7 @@
         <v>29167</v>
       </c>
       <c r="J226" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
         <v>7500</v>
       </c>
       <c r="J227" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>87500</v>
       </c>
       <c r="J228" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -12395,7 +12395,7 @@
         <v>7500</v>
       </c>
       <c r="J230" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -12447,7 +12447,7 @@
         <v>3750</v>
       </c>
       <c r="J231" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
         <v>87500</v>
       </c>
       <c r="J232" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -12551,7 +12551,7 @@
         <v>87500</v>
       </c>
       <c r="J233" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -12603,7 +12603,7 @@
         <v>87500</v>
       </c>
       <c r="J234" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -12655,7 +12655,7 @@
         <v>29167</v>
       </c>
       <c r="J235" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -12707,7 +12707,7 @@
         <v>29167</v>
       </c>
       <c r="J236" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
         <v>87500</v>
       </c>
       <c r="J237" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -12811,7 +12811,7 @@
         <v>84583</v>
       </c>
       <c r="J238" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K238" t="n">
         <v>3500</v>
@@ -12863,7 +12863,7 @@
         <v>58333</v>
       </c>
       <c r="J239" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -12915,7 +12915,7 @@
         <v>19000</v>
       </c>
       <c r="J240" t="n">
-        <v>27360</v>
+        <v>22800</v>
       </c>
       <c r="K240" t="n">
         <v>1200</v>
@@ -12967,7 +12967,7 @@
         <v>40000</v>
       </c>
       <c r="J241" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -13019,7 +13019,7 @@
         <v>120000</v>
       </c>
       <c r="J242" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>120000</v>
       </c>
       <c r="J243" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -13123,7 +13123,7 @@
         <v>58333</v>
       </c>
       <c r="J244" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -13175,7 +13175,7 @@
         <v>36000</v>
       </c>
       <c r="J245" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K245" t="n">
         <v>4800</v>
@@ -13227,7 +13227,7 @@
         <v>29000</v>
       </c>
       <c r="J246" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K246" t="n">
         <v>1200</v>
@@ -13279,7 +13279,7 @@
         <v>87500</v>
       </c>
       <c r="J247" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>11250</v>
       </c>
       <c r="J248" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -13383,7 +13383,7 @@
         <v>29167</v>
       </c>
       <c r="J249" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -13435,7 +13435,7 @@
         <v>40000</v>
       </c>
       <c r="J250" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -13487,7 +13487,7 @@
         <v>87500</v>
       </c>
       <c r="J251" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -13591,7 +13591,7 @@
         <v>11250</v>
       </c>
       <c r="J253" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -13643,7 +13643,7 @@
         <v>29167</v>
       </c>
       <c r="J254" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         <v>87500</v>
       </c>
       <c r="J255" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>76000</v>
       </c>
       <c r="J257" t="n">
-        <v>109440</v>
+        <v>91200</v>
       </c>
       <c r="K257" t="n">
         <v>4800</v>
@@ -13851,7 +13851,7 @@
         <v>80000</v>
       </c>
       <c r="J258" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
@@ -13903,7 +13903,7 @@
         <v>116000</v>
       </c>
       <c r="J259" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K259" t="n">
         <v>4800</v>
@@ -13955,7 +13955,7 @@
         <v>9000</v>
       </c>
       <c r="J260" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K260" t="n">
         <v>1200</v>
@@ -14007,7 +14007,7 @@
         <v>11250</v>
       </c>
       <c r="J261" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -14059,7 +14059,7 @@
         <v>58333</v>
       </c>
       <c r="J262" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -14111,7 +14111,7 @@
         <v>55417</v>
       </c>
       <c r="J263" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K263" t="n">
         <v>3500</v>
@@ -14163,7 +14163,7 @@
         <v>58333</v>
       </c>
       <c r="J264" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -14215,7 +14215,7 @@
         <v>58333</v>
       </c>
       <c r="J265" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K265" t="n">
         <v>0</v>
@@ -14267,7 +14267,7 @@
         <v>30000</v>
       </c>
       <c r="J266" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         <v>55417</v>
       </c>
       <c r="J267" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K267" t="n">
         <v>3500</v>
@@ -14371,7 +14371,7 @@
         <v>40000</v>
       </c>
       <c r="J268" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -14423,7 +14423,7 @@
         <v>11250</v>
       </c>
       <c r="J269" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -14475,7 +14475,7 @@
         <v>11250</v>
       </c>
       <c r="J270" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -14527,7 +14527,7 @@
         <v>3375</v>
       </c>
       <c r="J271" t="n">
-        <v>4860</v>
+        <v>4050</v>
       </c>
       <c r="K271" t="n">
         <v>450</v>
@@ -14579,7 +14579,7 @@
         <v>20000</v>
       </c>
       <c r="J272" t="n">
-        <v>28800</v>
+        <v>24000</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -14631,7 +14631,7 @@
         <v>3750</v>
       </c>
       <c r="J273" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -14683,7 +14683,7 @@
         <v>29167</v>
       </c>
       <c r="J274" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -14735,7 +14735,7 @@
         <v>58333</v>
       </c>
       <c r="J275" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         <v>58333</v>
       </c>
       <c r="J276" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -14839,7 +14839,7 @@
         <v>80000</v>
       </c>
       <c r="J277" t="n">
-        <v>115200</v>
+        <v>96000</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -14891,7 +14891,7 @@
         <v>36000</v>
       </c>
       <c r="J278" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K278" t="n">
         <v>4800</v>
@@ -14943,7 +14943,7 @@
         <v>55417</v>
       </c>
       <c r="J279" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K279" t="n">
         <v>3500</v>
@@ -14995,7 +14995,7 @@
         <v>116000</v>
       </c>
       <c r="J280" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K280" t="n">
         <v>4800</v>
@@ -15047,7 +15047,7 @@
         <v>29000</v>
       </c>
       <c r="J281" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K281" t="n">
         <v>1200</v>
@@ -15099,7 +15099,7 @@
         <v>87500</v>
       </c>
       <c r="J282" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -15151,7 +15151,7 @@
         <v>9000</v>
       </c>
       <c r="J283" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="K283" t="n">
         <v>1200</v>
@@ -15203,7 +15203,7 @@
         <v>19000</v>
       </c>
       <c r="J284" t="n">
-        <v>27360</v>
+        <v>22800</v>
       </c>
       <c r="K284" t="n">
         <v>1200</v>
@@ -15255,7 +15255,7 @@
         <v>36000</v>
       </c>
       <c r="J285" t="n">
-        <v>51840</v>
+        <v>43200</v>
       </c>
       <c r="K285" t="n">
         <v>4800</v>
@@ -15307,7 +15307,7 @@
         <v>58333</v>
       </c>
       <c r="J286" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -15359,7 +15359,7 @@
         <v>7500</v>
       </c>
       <c r="J287" t="n">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -15411,7 +15411,7 @@
         <v>120000</v>
       </c>
       <c r="J288" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -15463,7 +15463,7 @@
         <v>87500</v>
       </c>
       <c r="J289" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -15515,7 +15515,7 @@
         <v>58333</v>
       </c>
       <c r="J290" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>29167</v>
       </c>
       <c r="J291" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -15619,7 +15619,7 @@
         <v>120000</v>
       </c>
       <c r="J292" t="n">
-        <v>172800</v>
+        <v>144000</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -15671,7 +15671,7 @@
         <v>116000</v>
       </c>
       <c r="J293" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K293" t="n">
         <v>4800</v>
@@ -15723,7 +15723,7 @@
         <v>29167</v>
       </c>
       <c r="J294" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
         <v>55417</v>
       </c>
       <c r="J295" t="n">
-        <v>79800</v>
+        <v>66500</v>
       </c>
       <c r="K295" t="n">
         <v>3500</v>
@@ -15827,7 +15827,7 @@
         <v>11250</v>
       </c>
       <c r="J296" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -15879,7 +15879,7 @@
         <v>116000</v>
       </c>
       <c r="J297" t="n">
-        <v>167040</v>
+        <v>139200</v>
       </c>
       <c r="K297" t="n">
         <v>4800</v>
@@ -15931,7 +15931,7 @@
         <v>58333</v>
       </c>
       <c r="J298" t="n">
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -15983,7 +15983,7 @@
         <v>87500</v>
       </c>
       <c r="J299" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
         <v>40000</v>
       </c>
       <c r="J300" t="n">
-        <v>57600</v>
+        <v>48000</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>87500</v>
       </c>
       <c r="J301" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -16139,7 +16139,7 @@
         <v>29167</v>
       </c>
       <c r="J302" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -16191,7 +16191,7 @@
         <v>3750</v>
       </c>
       <c r="J303" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -16243,7 +16243,7 @@
         <v>26250</v>
       </c>
       <c r="J304" t="n">
-        <v>37800</v>
+        <v>31500</v>
       </c>
       <c r="K304" t="n">
         <v>3500</v>
@@ -16295,7 +16295,7 @@
         <v>11250</v>
       </c>
       <c r="J305" t="n">
-        <v>16200</v>
+        <v>13500</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -16347,7 +16347,7 @@
         <v>87500</v>
       </c>
       <c r="J306" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -16399,7 +16399,7 @@
         <v>3750</v>
       </c>
       <c r="J307" t="n">
-        <v>5400</v>
+        <v>4500</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -16451,7 +16451,7 @@
         <v>30000</v>
       </c>
       <c r="J308" t="n">
-        <v>43200</v>
+        <v>36000</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -16503,7 +16503,7 @@
         <v>84583</v>
       </c>
       <c r="J309" t="n">
-        <v>121800</v>
+        <v>101500</v>
       </c>
       <c r="K309" t="n">
         <v>3500</v>
@@ -16555,7 +16555,7 @@
         <v>87500</v>
       </c>
       <c r="J310" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -16607,7 +16607,7 @@
         <v>29000</v>
       </c>
       <c r="J311" t="n">
-        <v>41760</v>
+        <v>34800</v>
       </c>
       <c r="K311" t="n">
         <v>1200</v>
@@ -16659,7 +16659,7 @@
         <v>76000</v>
       </c>
       <c r="J312" t="n">
-        <v>109440</v>
+        <v>91200</v>
       </c>
       <c r="K312" t="n">
         <v>4800</v>
@@ -16711,7 +16711,7 @@
         <v>87500</v>
       </c>
       <c r="J313" t="n">
-        <v>126000</v>
+        <v>105000</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -16763,7 +16763,7 @@
         <v>7125</v>
       </c>
       <c r="J314" t="n">
-        <v>10260</v>
+        <v>8550</v>
       </c>
       <c r="K314" t="n">
         <v>450</v>
